--- a/human_validation/judge/kor/judge_D010_S001_P003__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D010_S001_P003__qwen3-235b_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B59"/>
+  <dimension ref="A1:B50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,250 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 진료실에 오신 것을 환영합니다. 오늘 어떤 일로 오셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 개럿의 목소리가 계속 들려서 왔어요. 그냥 기억 같은 게 아니고... 진짜 또렷하게, 마치 바로 뒤에 서 있는 것처럼 들려요. 등산로에 있을 때나 그림 작업실에 있을 때 그래요. 머릿속 한편으론 그 친구가 죽었다는 걸 알아요, 근데 그게 일어나고 있을 땐 완전히 진짜처럼 느껴지고, 그게 계속 저를 무섭게 해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 다른 사람들에게는 보이지 않는 것을 본 적이 있거나, 주변 사람들은 이해하거나 동의하지 않는데도 본인은 아주 강하게 믿었던 것이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 뭔가를 실제로 본 적은 없어요, 근데 개럿의 목소리는 들려요. 아주 또렷하게, 마치 바로 뒤에 서 있는 것처럼요—등산로에서든 그림 작업실에서든요. 적어도 제 일부는 그 친구가 죽었다는 걸 알아요, 근데 그게 일어나고 있는 순간에는 진짜처럼 느껴져요. 정말 진짜같이요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 다른 사람들에게는 보이지 않는 것을 본 적이 있거나, 주변 사람들은 이해하거나 동의하지 않는데도 본인은 아주 강하게 믿었던 것이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 맞아요, 네—이미 말씀드린 거 아는데, 그게 가장 중요한 부분이라서요. 개럿의 목소리가 아주 또렷하게 들려요, 마치 제 뒤에 서 있는 것처럼요. 등산로에서나 그림 작업실에서 그래요. 제 일부는 그 친구가 죽었다는 걸 알지만, 그 소리를 듣고 있을 땐 완전히 진짜처럼 느껴지고, 그게 저를 무섭게 만들어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 실제로는 없는 것을 본 적이 있거나, 스스로는 아주 강하게 느껴졌지만 다른 사람들은 공감하거나 이해하지 못했던 생각이나 믿음이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 네... 뭘 보는 건 아니에요, 사실. 근데 그 목소리—개럿의 목소리—가 문제예요. 계속 그 친구가 바로 뒤에 있는 것처럼 들려요, 특히 등산로에 있을 때나 그림 작업실에 있을 때요. 그 친구가 죽었다는 건 알아요, 근데 그게 일어날 때는 제가 상상하고 있다는 느낌이 안 들어요. 완전히 진짜처럼 느껴져요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 다른 사람들에게는 보이지 않는 것을 본 적이 있거나, 본인은 절대적으로 확신했지만 다른 사람들은 이해하거나 동의하지 못했던 믿음이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 네... 거의 아까 말씀드린 거랑 같아요. 뭔가를 실제로 보는 건 아닌데, 개럿의 목소리는 아주 또렷하게 들려요—마치 바로 뒤에 있는 것처럼, 등산로에서나 그림 작업실에서요. 제 일부는 그 친구가 죽었다는 걸 이해하고 있어요, 근데 그게 일어날 때는 완전히 진짜처럼 느껴져요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 개럿의 목소리를 듣는 것 말고, 실제로는 없는 것을 본 적이 있거나 주변 사람들이 공감하거나 이해하지 못했던 강한 믿음을 가진 적이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 아니요... 딱히 없는 것 같아요. 개럿의 목소리 말고는 그런 게 딱히 떠오르지 않아요. 뭔가를 보고 있지도 않고, 그런 믿음을 가진 적도 없는 것 같아요—적어도 제가 알아챈 건 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 배제됨: 망상장애 (D004); 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사 질문] 다른 사람들에게는 보이지 않는 것—예를 들어 형체나 사람, 물체 같은 것—을 본 적이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 환자 응답] 아니요, 실제로 없는 형체나 사람, 물체를 본 적은 없어요. 저한테는 시각적인 문제가 아니에요. 그 목소리—개럿의 목소리—가 진짜처럼 느껴지는 거예요, 마치 바로 뒤에 서 있는 것처럼요, 물론 제 일부는 그 친구가 거기 없다는 걸 알지만요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사의 감별진단] 배제됨: 망상장애 (D004); 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사 질문] 개럿의 목소리를 듣는 것 외에, 사실이 아닌 것을 확신했던 경험이나 다른 사람들은 보지 못하는 것을 본 적이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 환자 응답] 아니요, 그런 건 없는 것 같아요. 개럿의 목소리 말고는요. 뭔가를 확신했다가 나중에 사실이 아니었다는 걸 알게 된 순간도 없었고, 다른 사람들이 못 보는 걸 제가 보고 있는 것도 아니에요. 적어도 딱히 짚을 만한 건 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사의 감별진단] 배제됨: 망상장애 (D004); 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사 질문] 다른 사람들이 사실이 아니라고 말했거나, 나중에 본인이 사실이 아니었다는 걸 깨달았음에도 불구하고 완전히 확신했던 믿음이나 생각이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 환자 응답] 제가 아는 한은 없어요. 그러니까, 누구나 그렇듯 뭔가에 대해 틀린 적은 있죠, 근데 제가 완전히 확신했는데 사람들이 사실이 아니라고 말했거나, 나중에 그게 거짓이었다는 걸 그런 식으로 깨달았던 때는 딱히 떠오르지 않아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사의 감별진단] 배제됨: 망상장애 (D004); 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사 질문] 최소 2주 이상 기분이 가라앉거나 흥미를 잃어서 정상적으로 생활하기 힘들었던 적이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 환자 응답] 네. 그런 시기가 있었어요, 확실히 2주는 넘게요, 평소에 신경 쓰던 모든 게 그냥... 무덤덤해지는 거예요. 그림 그리기, 기타 연주, 극단 연습 가기—평소에 저를 지탱해주던 것들이 손에 닿지 않는 느낌이었어요. 환자들과 함께 있을 때도, 할 수는 있는데 그냥 형식적으로 하는 느낌이랄까요, 예전만큼 의미가 있지 않은 것처럼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사의 감별진단] 제2형 양극성장애 (D009); 주요우울장애 (D013); 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008) | 배제됨: 망상장애 (D004); 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사 질문] 평소보다 유난히 들뜨거나 흥분되거나 에너지가 넘쳤던 시기가 있으신가요—예를 들어 잠을 예전만큼 안 자도 되거나, 평소보다 말이 빨라지거나, 한꺼번에 많은 일을 벌이거나 하는 식으로요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 환자 응답] 네. 거의 불이 켜진 것처럼 느껴지는 때가 있었어요, 다른 사람들은 보지 못하는 어떤 다급한 목적이 저한테 있는 것처럼요. 처음엔 신났어요, 다른 모든 사람보다 더 빨리 움직이는 것 같은 느낌이었죠, 근데 누가 저한테 질문하거나 속도를 늦추려고 하면 금방 화가 났어요. 그냥 짜증나는 정도가 아니라—거의 폭발하는 것처럼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사의 감별진단] 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 외상후 스트레스장애 (D018) | 배제됨: 망상장애 (D004); 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>진단명: 정신병적 양상을 동반한 제1형 양극성장애 (D010)
 인구통계: 성별 남성 / 나이 41 / 직업상태 psychologist / 최종학력 학사
@@ -575,317 +810,47 @@
 증상 지속 기간: None
 추가 요건: delusions_and_hallucinations occur exclusively during the manic episode
 주호소 증상 코드: S020
-배경 서술: 개럿은 등산을 함께 다니고 지역 커뮤니티 극단에서 같이 자원봉사를 하던 가까운 친구가 갑작스럽게 세상을 떠나면서 큰 충격을 받았다. 이 상실은 그의 교우 관계와 창작 활동, 그리고 직업적 안정감에까지 영향을 미쳤다. 그 후 한 달 동안 그는 슬픔을 행동으로 승화시키려는 듯 야심 찬 치료 프로그램 아이디어를 구상하고, 추가로 멘토링을 맡고, 잠을 거의 자지 않았으며, 평소와 다르게 다급한 말투로 이야기하고, 산만함이 심해져 환자 기록을 안전하게 관리하지 못할 정도가 되었다. 이후 등산 중이나 그림 작업실에서 친구의 목소리가 들리기 시작했고, 뒤이어 그림과 기타 연주, 임상 업무에 대한 흥미를 완전히 잃는 무너짐이 찾아왔다. 수면과 식욕에 큰 변화가 생겼고, 정신운동 변화가 눈에 띄었으며, 극심한 피로감과 강한 죄책감, 반복되는 자살 사고가 나타났다. 그는 진료 예약을 취소하고 아내에게 더 이상 스스로 안전하게 지낼 자신이 없다고 말했고, 아내는 지역 위기상담 서비스에 연락했으며, 그는 정신과 입원 치료를 받게 되었다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 진료실에 오신 것을 환영합니다. 오늘 어떤 일로 오셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 개럿의 목소리가 계속 들려서 왔어요. 그냥 기억 같은 게 아니고... 진짜 또렷하게, 마치 바로 뒤에 서 있는 것처럼 들려요. 등산로에 있을 때나 그림 작업실에 있을 때 그래요. 머릿속 한편으론 그 친구가 죽었다는 걸 알아요, 근데 그게 일어나고 있을 땐 완전히 진짜처럼 느껴지고, 그게 계속 저를 무섭게 해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 다른 사람들에게는 보이지 않는 것을 본 적이 있거나, 주변 사람들은 이해하거나 동의하지 않는데도 본인은 아주 강하게 믿었던 것이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 뭔가를 실제로 본 적은 없어요, 근데 개럿의 목소리는 들려요. 아주 또렷하게, 마치 바로 뒤에 서 있는 것처럼요—등산로에서든 그림 작업실에서든요. 적어도 제 일부는 그 친구가 죽었다는 걸 알아요, 근데 그게 일어나고 있는 순간에는 진짜처럼 느껴져요. 정말 진짜같이요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 다른 사람들에게는 보이지 않는 것을 본 적이 있거나, 주변 사람들은 이해하거나 동의하지 않는데도 본인은 아주 강하게 믿었던 것이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 맞아요, 네—이미 말씀드린 거 아는데, 그게 가장 중요한 부분이라서요. 개럿의 목소리가 아주 또렷하게 들려요, 마치 제 뒤에 서 있는 것처럼요. 등산로에서나 그림 작업실에서 그래요. 제 일부는 그 친구가 죽었다는 걸 알지만, 그 소리를 듣고 있을 땐 완전히 진짜처럼 느껴지고, 그게 저를 무섭게 만들어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 실제로는 없는 것을 본 적이 있거나, 스스로는 아주 강하게 느껴졌지만 다른 사람들은 공감하거나 이해하지 못했던 생각이나 믿음이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 네... 뭘 보는 건 아니에요, 사실. 근데 그 목소리—개럿의 목소리—가 문제예요. 계속 그 친구가 바로 뒤에 있는 것처럼 들려요, 특히 등산로에 있을 때나 그림 작업실에 있을 때요. 그 친구가 죽었다는 건 알아요, 근데 그게 일어날 때는 제가 상상하고 있다는 느낌이 안 들어요. 완전히 진짜처럼 느껴져요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 다른 사람들에게는 보이지 않는 것을 본 적이 있거나, 본인은 절대적으로 확신했지만 다른 사람들은 이해하거나 동의하지 못했던 믿음이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 네... 거의 아까 말씀드린 거랑 같아요. 뭔가를 실제로 보는 건 아닌데, 개럿의 목소리는 아주 또렷하게 들려요—마치 바로 뒤에 있는 것처럼, 등산로에서나 그림 작업실에서요. 제 일부는 그 친구가 죽었다는 걸 이해하고 있어요, 근데 그게 일어날 때는 완전히 진짜처럼 느껴져요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 개럿의 목소리를 듣는 것 말고, 실제로는 없는 것을 본 적이 있거나 주변 사람들이 공감하거나 이해하지 못했던 강한 믿음을 가진 적이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 아니요... 딱히 없는 것 같아요. 개럿의 목소리 말고는 그런 게 딱히 떠오르지 않아요. 뭔가를 보고 있지도 않고, 그런 믿음을 가진 적도 없는 것 같아요—적어도 제가 알아챈 건 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사의 감별진단] 배제됨: 망상장애 (D004); 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사 질문] 다른 사람들에게는 보이지 않는 것—예를 들어 형체나 사람, 물체 같은 것—을 본 적이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 환자 응답] 아니요, 실제로 없는 형체나 사람, 물체를 본 적은 없어요. 저한테는 시각적인 문제가 아니에요. 그 목소리—개럿의 목소리—가 진짜처럼 느껴지는 거예요, 마치 바로 뒤에 서 있는 것처럼요, 물론 제 일부는 그 친구가 거기 없다는 걸 알지만요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사의 감별진단] 배제됨: 망상장애 (D004); 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사 질문] 개럿의 목소리를 듣는 것 외에, 사실이 아닌 것을 확신했던 경험이나 다른 사람들은 보지 못하는 것을 본 적이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 환자 응답] 아니요, 그런 건 없는 것 같아요. 개럿의 목소리 말고는요. 뭔가를 확신했다가 나중에 사실이 아니었다는 걸 알게 된 순간도 없었고, 다른 사람들이 못 보는 걸 제가 보고 있는 것도 아니에요. 적어도 딱히 짚을 만한 건 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사의 감별진단] 배제됨: 망상장애 (D004); 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사 질문] 다른 사람들이 사실이 아니라고 말했거나, 나중에 본인이 사실이 아니었다는 걸 깨달았음에도 불구하고 완전히 확신했던 믿음이나 생각이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 환자 응답] 제가 아는 한은 없어요. 그러니까, 누구나 그렇듯 뭔가에 대해 틀린 적은 있죠, 근데 제가 완전히 확신했는데 사람들이 사실이 아니라고 말했거나, 나중에 그게 거짓이었다는 걸 그런 식으로 깨달았던 때는 딱히 떠오르지 않아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사의 감별진단] 배제됨: 망상장애 (D004); 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사 질문] 최소 2주 이상 기분이 가라앉거나 흥미를 잃어서 정상적으로 생활하기 힘들었던 적이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 환자 응답] 네. 그런 시기가 있었어요, 확실히 2주는 넘게요, 평소에 신경 쓰던 모든 게 그냥... 무덤덤해지는 거예요. 그림 그리기, 기타 연주, 극단 연습 가기—평소에 저를 지탱해주던 것들이 손에 닿지 않는 느낌이었어요. 환자들과 함께 있을 때도, 할 수는 있는데 그냥 형식적으로 하는 느낌이랄까요, 예전만큼 의미가 있지 않은 것처럼요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사의 감별진단] 중간확률: 제2형 양극성장애 (D009); 주요우울장애 (D013); 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008) | 배제됨: 망상장애 (D004); 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사 질문] 평소보다 유난히 들뜨거나 흥분되거나 에너지가 넘쳤던 시기가 있으신가요—예를 들어 잠을 예전만큼 안 자도 되거나, 평소보다 말이 빨라지거나, 한꺼번에 많은 일을 벌이거나 하는 식으로요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 환자 응답] 네. 거의 불이 켜진 것처럼 느껴지는 때가 있었어요, 다른 사람들은 보지 못하는 어떤 다급한 목적이 저한테 있는 것처럼요. 처음엔 신났어요, 다른 모든 사람보다 더 빨리 움직이는 것 같은 느낌이었죠, 근데 누가 저한테 질문하거나 속도를 늦추려고 하면 금방 화가 났어요. 그냥 짜증나는 정도가 아니라—거의 폭발하는 것처럼요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
+배경 서술: 개럿은 등산을 함께 다니고 지역 커뮤니티 극단에서 같이 자원봉사를 하던 가까운 친구가 갑작스럽게 세상을 떠나면서 큰 충격을 받았다. 이 상실은 그의 교우 관계와 창작 활동, 그리고 직업적 안정감에까지 영향을 미쳤다. 그 후 한 달 동안 그는 슬픔을 행동으로 승화시키려는 듯 야심 찬 치료 프로그램 아이디어를 구상하고, 추가로 멘토링을 맡고, 잠을 거의 자지 않았으며, 평소와 다르게 다급한 말투로 이야기하고, 산만함이 심해져 환자 기록을 안전하게 관리하지 못할 정도가 되었다. 이후 등산 중이나 그림 작업실에서 친구의 목소리가 들리기 시작했고, 뒤이어 그림과 기타 연주, 임상 업무에 대한 흥미를 완전히 잃는 무너짐이 찾아왔다. 수면과 식욕에 큰 변화가 생겼고, 정신운동 변화가 눈에 띄었으며, 극심한 피로감과 강한 죄책감, 반복되는 자살 사고가 나타났다. 그는 진료 예약을 취소하고 아내에게 더 이상 스스로 안전하게 지낼 자신이 없다고 말했고, 아내는 지역 위기상담 서비스에 연락했으며, 그는 정신과 입원 치료를 받게 되었다.
+표집된 증상 목록:
+  - S020 환각: 외부 자극 없이 발생하지만 정상적인 지각만큼 생생하고 뚜렷한 지각 경험.
+  - S025 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.
+  - S026 체중/식욕 변화: 식욕이나 체중의 현저한 증가 또는 감소.
+  - S027 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.
+  - S028 정신운동 변화: 관찰 가능한 정신운동 활동의 증가 또는 감소.
+  - S029 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.
+  - S030 무가치감/죄책감: 무가치감이나 과도하거나 부적절한 죄책감(망상적일 수도 있으며, 단순히 아픈 것에 대한 자책이 아님).
+  - S032 죽음/자살: 반복되는 죽음에 대한 생각, 반복되는 자살 사고, 또는 자살 시도.
+  - S033 상승/과민한 기분: 비정상적이고 지속적으로 고양되거나 팽창되거나 과민한 기분이 뚜렷하게 나타나는 기간.
+  - S034 활동 증가: 비정상적이고 지속적으로 증가한 목표지향적 활동이나 에너지.
+  - S037 압박된 언어: 평소보다 말이 많아지거나 계속 말하려는 압박감을 느낌.
+  - S038 사고의 질주: 사고의 비약이나 생각이 질주하는 듯한 주관적 경험.
+  - S039 조증성 산만함: 중요하지 않거나 관련 없는 외부 자극에 지나치게 쉽게 주의가 쏠림.</t>
+        </is>
+      </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>[11번째 턴 · 의사의 감별진단] 중간확률: 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 외상후 스트레스장애 (D018) | 배제됨: 망상장애 (D004); 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: None (None, ICD: F31.6)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: manic_episode (관계=must_include, 요구개수=5, 충족개수=1, 커버리지=0.2)
-  확인된 근거: 상승/과민한 기분: 비정상적이고 지속적으로 고양되거나 팽창되거나 과민한 기분이 뚜렷하게 나타나는 기간.
-  누락: 활동 증가: 비정상적이고 지속적으로 증가한 목표지향적 활동이나 에너지.; 과장된 자존감: 과장된 자존감이나 과대성(단순한 자신감 과잉부터 망상적 수준까지 다양할 수 있음).; 수면 욕구 감소: 수면 욕구가 감소함(예: 단 3시간만 자도 개운함을 느낌).; 압박된 언어: 평소보다 말이 많아지거나 계속 말하려는 압박감을 느낌.; 사고의 질주: 사고의 비약이나 생각이 질주하는 듯한 주관적 경험.; 조증성 산만함: 중요하지 않거나 관련 없는 외부 자극에 지나치게 쉽게 주의가 쏠림.; 목표지향 활동 증가: 목표지향적 활동(직장, 학업, 사회, 성적 영역)의 증가 또는 목적 없는 정신운동 초조.; 위험 결과 초래 행동: 고통스러운 결과를 초래할 가능성이 높은 활동에 지나치게 몰두함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: depressive_episode (관계=include, 요구개수=5, 충족개수=1, 커버리지=0.2)
-  확인된 근거: 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.
-  누락: 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.; 체중/식욕 변화: 식욕이나 체중의 현저한 증가 또는 감소.; 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.; 정신운동 변화: 관찰 가능한 정신운동 활동의 증가 또는 감소.; 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.; 무가치감/죄책감: 무가치감이나 과도하거나 부적절한 죄책감(망상적일 수도 있으며, 단순히 아픈 것에 대한 자책이 아님).; 사고력 저하: 사고력이나 집중력 저하, 또는 우유부단함.; 죽음/자살: 반복되는 죽음에 대한 생각, 반복되는 자살 사고, 또는 자살 시도.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: delusions_and_hallucinations (관계=must_include, 요구개수=1, 충족개수=1, 커버리지=1.0)
-  확인된 근거: 환각: 외부 자극 없이 발생하지만 정상적인 지각만큼 생생하고 뚜렷한 지각 경험.
-  누락: 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.</t>
+          <t>의사의 최종 진단: None (None, ICD: F31.6)
+지속 기간 요건: None
+기능적 손상 요건: None
+추가 요건: 없음
+체크리스트 그룹: manic_episode (관계=must_include, 요구개수=5, 충족개수=1, 커버리지=0.2)
+확인된 근거:
+  - 상승/과민한 기분: 비정상적이고 지속적으로 고양되거나 팽창되거나 과민한 기분이 뚜렷하게 나타나는 기간.
+체크리스트 그룹: depressive_episode (관계=include, 요구개수=5, 충족개수=1, 커버리지=0.2)
+확인된 근거:
+  - 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.
+체크리스트 그룹: delusions_and_hallucinations (관계=must_include, 요구개수=1, 충족개수=1, 커버리지=1.0)
+확인된 근거:
+  - 환각: 외부 자극 없이 발생하지만 정상적인 지각만큼 생생하고 뚜렷한 지각 경험.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="A49:B49"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D010_S001_P003__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D010_S001_P003__qwen3-235b_kor.xlsx
@@ -796,6 +796,11 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -846,11 +851,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A49:B49"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D010_S001_P003__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D010_S001_P003__qwen3-235b_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0.2</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
